--- a/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$285</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9053" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="834">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2125,6 +2125,42 @@
     <t>Organization.telecom:mailbox-mss.extension:emailType</t>
   </si>
   <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.url</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.url</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/StructureDefinition/FrContactPointEmailType</t>
+  </si>
+  <si>
+    <t>Organization.telecom:mailbox-mss.extension:emailType.value[x]</t>
+  </si>
+  <si>
+    <t>Organization.telecom.extension.value[x]</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R256-TypeMessagerie/FHIR/TRE-R256-TypeMessagerie"/&gt;
+  &lt;code value="MSSANTE"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>http://interopsante.org/fhir/ValueSet/fr-email-type</t>
+  </si>
+  <si>
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata</t>
   </si>
   <si>
@@ -2144,13 +2180,7 @@
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.id</t>
   </si>
   <si>
-    <t>Organization.telecom.extension.id</t>
-  </si>
-  <si>
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.extension</t>
   </si>
   <si>
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:type</t>
@@ -2315,16 +2345,10 @@
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.url</t>
   </si>
   <si>
-    <t>Organization.telecom.extension.url</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
   </si>
   <si>
     <t>Organization.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>
-  </si>
-  <si>
-    <t>Organization.telecom.extension.value[x]</t>
   </si>
   <si>
     <t>base64Binary
@@ -2909,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ281"/>
+  <dimension ref="A1:AJ285"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="97.4375" customWidth="true" bestFit="true"/>
@@ -25274,7 +25298,7 @@
         <v>637</v>
       </c>
       <c r="D219" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
@@ -25301,9 +25325,7 @@
       <c r="M219" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N219" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N219" s="2"/>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>73</v>
@@ -25372,11 +25394,9 @@
         <v>678</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C220" t="s" s="2">
         <v>679</v>
       </c>
+      <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
         <v>73</v>
       </c>
@@ -25388,7 +25408,7 @@
         <v>81</v>
       </c>
       <c r="H220" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I220" t="s" s="2">
         <v>73</v>
@@ -25397,13 +25417,13 @@
         <v>73</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>680</v>
+        <v>96</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>681</v>
+        <v>97</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>682</v>
+        <v>98</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -25454,27 +25474,27 @@
         <v>73</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -25485,7 +25505,7 @@
         <v>74</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>73</v>
@@ -25497,13 +25517,13 @@
         <v>73</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -25542,50 +25562,50 @@
         <v>73</v>
       </c>
       <c r="AB221" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC221" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD221" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE221" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>73</v>
@@ -25597,16 +25617,16 @@
         <v>73</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
@@ -25614,7 +25634,7 @@
       </c>
       <c r="Q222" s="2"/>
       <c r="R222" t="s" s="2">
-        <v>73</v>
+        <v>684</v>
       </c>
       <c r="S222" t="s" s="2">
         <v>73</v>
@@ -25644,43 +25664,41 @@
         <v>73</v>
       </c>
       <c r="AB222" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC222" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD222" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE222" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="C223" t="s" s="2">
-        <v>688</v>
-      </c>
+      <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
         <v>73</v>
       </c>
@@ -25701,13 +25719,13 @@
         <v>73</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>689</v>
+        <v>213</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>494</v>
+        <v>214</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -25719,7 +25737,7 @@
         <v>73</v>
       </c>
       <c r="S223" t="s" s="2">
-        <v>73</v>
+        <v>687</v>
       </c>
       <c r="T223" t="s" s="2">
         <v>73</v>
@@ -25734,13 +25752,11 @@
         <v>73</v>
       </c>
       <c r="X223" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y223" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>73</v>
+        <v>688</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>73</v>
@@ -25758,29 +25774,31 @@
         <v>73</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH223" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI223" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C224" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="B224" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
         <v>73</v>
       </c>
@@ -25801,13 +25819,13 @@
         <v>73</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>96</v>
+        <v>691</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>97</v>
+        <v>692</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>98</v>
+        <v>693</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -25858,27 +25876,27 @@
         <v>73</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25889,7 +25907,7 @@
         <v>74</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>73</v>
@@ -25901,13 +25919,13 @@
         <v>73</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>493</v>
+        <v>97</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -25946,50 +25964,50 @@
         <v>73</v>
       </c>
       <c r="AB225" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC225" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD225" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE225" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H226" t="s" s="2">
         <v>73</v>
@@ -26001,16 +26019,16 @@
         <v>73</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
@@ -26018,7 +26036,7 @@
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" t="s" s="2">
-        <v>688</v>
+        <v>73</v>
       </c>
       <c r="S226" t="s" s="2">
         <v>73</v>
@@ -26048,31 +26066,31 @@
         <v>73</v>
       </c>
       <c r="AB226" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC226" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD226" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE226" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>209</v>
+        <v>109</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="227" hidden="true">
@@ -26080,9 +26098,11 @@
         <v>696</v>
       </c>
       <c r="B227" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C227" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
         <v>73</v>
       </c>
@@ -26103,13 +26123,13 @@
         <v>73</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>290</v>
+        <v>102</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>213</v>
+        <v>698</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -26136,11 +26156,13 @@
         <v>73</v>
       </c>
       <c r="X227" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Y227" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y227" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z227" t="s" s="2">
-        <v>698</v>
+        <v>73</v>
       </c>
       <c r="AA227" t="s" s="2">
         <v>73</v>
@@ -26158,19 +26180,19 @@
         <v>73</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI227" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="228" hidden="true">
@@ -26178,11 +26200,9 @@
         <v>699</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C228" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
         <v>73</v>
       </c>
@@ -26203,13 +26223,13 @@
         <v>73</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>700</v>
+        <v>97</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -26260,19 +26280,19 @@
         <v>73</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI228" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="229" hidden="true">
@@ -26280,7 +26300,7 @@
         <v>701</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -26291,7 +26311,7 @@
         <v>74</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>73</v>
@@ -26303,13 +26323,13 @@
         <v>73</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -26348,39 +26368,39 @@
         <v>73</v>
       </c>
       <c r="AB229" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC229" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD229" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE229" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -26388,10 +26408,10 @@
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>73</v>
@@ -26403,22 +26423,24 @@
         <v>73</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N230" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N230" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q230" s="2"/>
       <c r="R230" t="s" s="2">
-        <v>73</v>
+        <v>697</v>
       </c>
       <c r="S230" t="s" s="2">
         <v>73</v>
@@ -26448,39 +26470,39 @@
         <v>73</v>
       </c>
       <c r="AB230" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC230" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD230" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE230" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -26488,7 +26510,7 @@
       </c>
       <c r="E231" s="2"/>
       <c r="F231" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G231" t="s" s="2">
         <v>81</v>
@@ -26503,24 +26525,22 @@
         <v>73</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N231" s="2"/>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="S231" t="s" s="2">
         <v>73</v>
@@ -26538,13 +26558,11 @@
         <v>73</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y231" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Y231" s="2"/>
       <c r="Z231" t="s" s="2">
-        <v>73</v>
+        <v>707</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>73</v>
@@ -26562,29 +26580,31 @@
         <v>73</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C232" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C232" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="D232" t="s" s="2">
         <v>73</v>
       </c>
@@ -26605,13 +26625,13 @@
         <v>73</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>213</v>
+        <v>709</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -26662,31 +26682,29 @@
         <v>73</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C233" t="s" s="2">
-        <v>706</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
         <v>73</v>
       </c>
@@ -26695,7 +26713,7 @@
         <v>74</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>73</v>
@@ -26707,13 +26725,13 @@
         <v>73</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>493</v>
+        <v>97</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -26764,27 +26782,27 @@
         <v>73</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26795,7 +26813,7 @@
         <v>74</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>73</v>
@@ -26807,13 +26825,13 @@
         <v>73</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -26852,39 +26870,39 @@
         <v>73</v>
       </c>
       <c r="AB234" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC234" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD234" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE234" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -26892,10 +26910,10 @@
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H235" t="s" s="2">
         <v>73</v>
@@ -26907,22 +26925,24 @@
         <v>73</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N235" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N235" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>73</v>
@@ -26952,39 +26972,39 @@
         <v>73</v>
       </c>
       <c r="AB235" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC235" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD235" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE235" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26992,7 +27012,7 @@
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G236" t="s" s="2">
         <v>81</v>
@@ -27007,24 +27027,22 @@
         <v>73</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N236" s="2"/>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q236" s="2"/>
       <c r="R236" t="s" s="2">
-        <v>706</v>
+        <v>73</v>
       </c>
       <c r="S236" t="s" s="2">
         <v>73</v>
@@ -27066,29 +27084,31 @@
         <v>73</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C237" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C237" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="D237" t="s" s="2">
         <v>73</v>
       </c>
@@ -27097,7 +27117,7 @@
         <v>74</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>73</v>
@@ -27109,13 +27129,13 @@
         <v>73</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>213</v>
+        <v>493</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -27166,31 +27186,29 @@
         <v>73</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
         <v>73</v>
       </c>
@@ -27211,13 +27229,13 @@
         <v>73</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>713</v>
+        <v>97</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -27268,27 +27286,27 @@
         <v>73</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -27299,7 +27317,7 @@
         <v>74</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>73</v>
@@ -27311,13 +27329,13 @@
         <v>73</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -27356,39 +27374,39 @@
         <v>73</v>
       </c>
       <c r="AB239" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC239" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD239" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE239" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -27396,10 +27414,10 @@
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>73</v>
@@ -27411,22 +27429,24 @@
         <v>73</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N240" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>73</v>
+        <v>715</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>73</v>
@@ -27456,39 +27476,39 @@
         <v>73</v>
       </c>
       <c r="AB240" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC240" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD240" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE240" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -27496,7 +27516,7 @@
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G241" t="s" s="2">
         <v>81</v>
@@ -27511,24 +27531,22 @@
         <v>73</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N241" s="2"/>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q241" s="2"/>
       <c r="R241" t="s" s="2">
-        <v>712</v>
+        <v>73</v>
       </c>
       <c r="S241" t="s" s="2">
         <v>73</v>
@@ -27570,29 +27588,31 @@
         <v>73</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C242" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C242" t="s" s="2">
+        <v>721</v>
+      </c>
       <c r="D242" t="s" s="2">
         <v>73</v>
       </c>
@@ -27613,13 +27633,13 @@
         <v>73</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>213</v>
+        <v>722</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -27670,31 +27690,29 @@
         <v>73</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH242" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI242" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C243" t="s" s="2">
-        <v>719</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
         <v>73</v>
       </c>
@@ -27703,7 +27721,7 @@
         <v>74</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>73</v>
@@ -27715,13 +27733,13 @@
         <v>73</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>493</v>
+        <v>97</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -27772,27 +27790,27 @@
         <v>73</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH243" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27803,7 +27821,7 @@
         <v>74</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>73</v>
@@ -27815,13 +27833,13 @@
         <v>73</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -27860,39 +27878,39 @@
         <v>73</v>
       </c>
       <c r="AB244" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC244" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD244" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE244" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27900,10 +27918,10 @@
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>73</v>
@@ -27915,22 +27933,24 @@
         <v>73</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N245" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N245" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>73</v>
+        <v>721</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>73</v>
@@ -27960,39 +27980,39 @@
         <v>73</v>
       </c>
       <c r="AB245" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC245" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD245" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE245" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI245" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -28000,7 +28020,7 @@
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G246" t="s" s="2">
         <v>81</v>
@@ -28015,24 +28035,22 @@
         <v>73</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N246" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N246" s="2"/>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q246" s="2"/>
       <c r="R246" t="s" s="2">
-        <v>719</v>
+        <v>73</v>
       </c>
       <c r="S246" t="s" s="2">
         <v>73</v>
@@ -28074,29 +28092,31 @@
         <v>73</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH246" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ246" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C247" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C247" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="D247" t="s" s="2">
         <v>73</v>
       </c>
@@ -28105,7 +28125,7 @@
         <v>74</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H247" t="s" s="2">
         <v>73</v>
@@ -28117,13 +28137,13 @@
         <v>73</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>213</v>
+        <v>493</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -28174,31 +28194,29 @@
         <v>73</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH247" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI247" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ247" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C248" t="s" s="2">
-        <v>725</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
         <v>73</v>
       </c>
@@ -28219,13 +28237,13 @@
         <v>73</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>726</v>
+        <v>97</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -28276,27 +28294,27 @@
         <v>73</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH248" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ248" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -28307,7 +28325,7 @@
         <v>74</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H249" t="s" s="2">
         <v>73</v>
@@ -28319,13 +28337,13 @@
         <v>73</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -28364,39 +28382,39 @@
         <v>73</v>
       </c>
       <c r="AB249" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC249" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD249" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE249" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH249" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ249" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -28404,10 +28422,10 @@
       </c>
       <c r="E250" s="2"/>
       <c r="F250" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H250" t="s" s="2">
         <v>73</v>
@@ -28419,22 +28437,24 @@
         <v>73</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N250" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N250" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O250" s="2"/>
       <c r="P250" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q250" s="2"/>
       <c r="R250" t="s" s="2">
-        <v>73</v>
+        <v>728</v>
       </c>
       <c r="S250" t="s" s="2">
         <v>73</v>
@@ -28464,39 +28484,39 @@
         <v>73</v>
       </c>
       <c r="AB250" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC250" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD250" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE250" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG250" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH250" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ250" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -28504,7 +28524,7 @@
       </c>
       <c r="E251" s="2"/>
       <c r="F251" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G251" t="s" s="2">
         <v>81</v>
@@ -28519,24 +28539,22 @@
         <v>73</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N251" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N251" s="2"/>
       <c r="O251" s="2"/>
       <c r="P251" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q251" s="2"/>
       <c r="R251" t="s" s="2">
-        <v>725</v>
+        <v>73</v>
       </c>
       <c r="S251" t="s" s="2">
         <v>73</v>
@@ -28578,29 +28596,31 @@
         <v>73</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG251" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH251" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI251" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ251" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C252" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C252" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="D252" t="s" s="2">
         <v>73</v>
       </c>
@@ -28621,13 +28641,13 @@
         <v>73</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>390</v>
+        <v>102</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>213</v>
+        <v>735</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" s="2"/>
@@ -28678,31 +28698,29 @@
         <v>73</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH252" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI252" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ252" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="C253" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
         <v>73</v>
       </c>
@@ -28723,13 +28741,13 @@
         <v>73</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>733</v>
+        <v>97</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>494</v>
+        <v>98</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -28780,27 +28798,27 @@
         <v>73</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH253" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI253" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ253" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -28811,7 +28829,7 @@
         <v>74</v>
       </c>
       <c r="G254" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H254" t="s" s="2">
         <v>73</v>
@@ -28823,13 +28841,13 @@
         <v>73</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>98</v>
+        <v>494</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -28868,39 +28886,39 @@
         <v>73</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC254" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD254" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ254" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -28908,10 +28926,10 @@
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>73</v>
@@ -28923,22 +28941,24 @@
         <v>73</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N255" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q255" s="2"/>
       <c r="R255" t="s" s="2">
-        <v>73</v>
+        <v>734</v>
       </c>
       <c r="S255" t="s" s="2">
         <v>73</v>
@@ -28968,39 +28988,39 @@
         <v>73</v>
       </c>
       <c r="AB255" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC255" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD255" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE255" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="AG255" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -29008,7 +29028,7 @@
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G256" t="s" s="2">
         <v>81</v>
@@ -29023,24 +29043,22 @@
         <v>73</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N256" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N256" s="2"/>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q256" s="2"/>
       <c r="R256" t="s" s="2">
-        <v>732</v>
+        <v>73</v>
       </c>
       <c r="S256" t="s" s="2">
         <v>73</v>
@@ -29082,29 +29100,31 @@
         <v>73</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AG256" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="C257" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C257" t="s" s="2">
+        <v>741</v>
+      </c>
       <c r="D257" t="s" s="2">
         <v>73</v>
       </c>
@@ -29125,13 +29145,13 @@
         <v>73</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>390</v>
+        <v>102</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>213</v>
+        <v>742</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -29182,27 +29202,27 @@
         <v>73</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>739</v>
+        <v>700</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -29210,7 +29230,7 @@
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G258" t="s" s="2">
         <v>81</v>
@@ -29225,24 +29245,22 @@
         <v>73</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>205</v>
+        <v>97</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N258" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N258" s="2"/>
       <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q258" s="2"/>
       <c r="R258" t="s" s="2">
-        <v>740</v>
+        <v>73</v>
       </c>
       <c r="S258" t="s" s="2">
         <v>73</v>
@@ -29284,10 +29302,10 @@
         <v>73</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="AG258" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH258" t="s" s="2">
         <v>81</v>
@@ -29301,10 +29319,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -29327,13 +29345,13 @@
         <v>73</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>743</v>
+        <v>102</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>213</v>
+        <v>493</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="N259" s="2"/>
       <c r="O259" s="2"/>
@@ -29372,39 +29390,39 @@
         <v>73</v>
       </c>
       <c r="AB259" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC259" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD259" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE259" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH259" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI259" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ259" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>640</v>
+        <v>704</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -29424,19 +29442,19 @@
         <v>73</v>
       </c>
       <c r="J260" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>641</v>
+        <v>205</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>642</v>
+        <v>206</v>
       </c>
       <c r="N260" t="s" s="2">
-        <v>379</v>
+        <v>207</v>
       </c>
       <c r="O260" s="2"/>
       <c r="P260" t="s" s="2">
@@ -29444,10 +29462,10 @@
       </c>
       <c r="Q260" s="2"/>
       <c r="R260" t="s" s="2">
-        <v>73</v>
+        <v>741</v>
       </c>
       <c r="S260" t="s" s="2">
-        <v>745</v>
+        <v>73</v>
       </c>
       <c r="T260" t="s" s="2">
         <v>73</v>
@@ -29462,13 +29480,13 @@
         <v>73</v>
       </c>
       <c r="X260" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y260" t="s" s="2">
-        <v>643</v>
+        <v>73</v>
       </c>
       <c r="Z260" t="s" s="2">
-        <v>644</v>
+        <v>73</v>
       </c>
       <c r="AA260" t="s" s="2">
         <v>73</v>
@@ -29486,19 +29504,19 @@
         <v>73</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>645</v>
+        <v>209</v>
       </c>
       <c r="AG260" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH260" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>646</v>
+        <v>73</v>
       </c>
       <c r="AJ260" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="261" hidden="true">
@@ -29506,7 +29524,7 @@
         <v>746</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -29514,35 +29532,31 @@
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G261" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H261" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I261" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J261" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>96</v>
+        <v>390</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>747</v>
+        <v>213</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N261" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O261" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N261" s="2"/>
+      <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
         <v>73</v>
       </c>
@@ -29590,7 +29604,7 @@
         <v>73</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>652</v>
+        <v>215</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>74</v>
@@ -29607,10 +29621,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -29618,7 +29632,7 @@
       </c>
       <c r="E262" s="2"/>
       <c r="F262" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G262" t="s" s="2">
         <v>81</v>
@@ -29627,32 +29641,30 @@
         <v>73</v>
       </c>
       <c r="I262" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J262" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>654</v>
+        <v>205</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>655</v>
+        <v>206</v>
       </c>
       <c r="N262" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O262" t="s" s="2">
-        <v>657</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O262" s="2"/>
       <c r="P262" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q262" s="2"/>
       <c r="R262" t="s" s="2">
-        <v>73</v>
+        <v>748</v>
       </c>
       <c r="S262" t="s" s="2">
         <v>73</v>
@@ -29670,13 +29682,13 @@
         <v>73</v>
       </c>
       <c r="X262" t="s" s="2">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="Y262" t="s" s="2">
-        <v>658</v>
+        <v>73</v>
       </c>
       <c r="Z262" t="s" s="2">
-        <v>659</v>
+        <v>73</v>
       </c>
       <c r="AA262" t="s" s="2">
         <v>73</v>
@@ -29694,27 +29706,27 @@
         <v>73</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>660</v>
+        <v>209</v>
       </c>
       <c r="AG262" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH262" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -29725,7 +29737,7 @@
         <v>74</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H263" t="s" s="2">
         <v>73</v>
@@ -29734,20 +29746,18 @@
         <v>73</v>
       </c>
       <c r="J263" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>662</v>
+        <v>750</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>663</v>
+        <v>213</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N263" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N263" s="2"/>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
         <v>73</v>
@@ -29796,7 +29806,7 @@
         <v>73</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>666</v>
+        <v>215</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>74</v>
@@ -29816,7 +29826,7 @@
         <v>751</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -29824,10 +29834,10 @@
       </c>
       <c r="E264" s="2"/>
       <c r="F264" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G264" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H264" t="s" s="2">
         <v>73</v>
@@ -29839,16 +29849,16 @@
         <v>82</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>668</v>
+        <v>641</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>669</v>
+        <v>642</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>314</v>
+        <v>379</v>
       </c>
       <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
@@ -29859,7 +29869,7 @@
         <v>73</v>
       </c>
       <c r="S264" t="s" s="2">
-        <v>73</v>
+        <v>752</v>
       </c>
       <c r="T264" t="s" s="2">
         <v>73</v>
@@ -29874,13 +29884,13 @@
         <v>73</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="Y264" t="s" s="2">
-        <v>73</v>
+        <v>643</v>
       </c>
       <c r="Z264" t="s" s="2">
-        <v>73</v>
+        <v>644</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>73</v>
@@ -29898,7 +29908,7 @@
         <v>73</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>74</v>
@@ -29907,18 +29917,18 @@
         <v>81</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>93</v>
+        <v>646</v>
       </c>
       <c r="AJ264" t="s" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>752</v>
+        <v>647</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29926,10 +29936,10 @@
       </c>
       <c r="E265" s="2"/>
       <c r="F265" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G265" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H265" t="s" s="2">
         <v>82</v>
@@ -29938,22 +29948,22 @@
         <v>73</v>
       </c>
       <c r="J265" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>753</v>
+        <v>96</v>
       </c>
       <c r="L265" t="s" s="2">
         <v>754</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>755</v>
+        <v>649</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>756</v>
+        <v>650</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>757</v>
+        <v>651</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>73</v>
@@ -30002,27 +30012,27 @@
         <v>73</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>752</v>
+        <v>652</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH265" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI265" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ265" t="s" s="2">
-        <v>758</v>
+        <v>94</v>
       </c>
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>759</v>
+        <v>653</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -30039,25 +30049,25 @@
         <v>73</v>
       </c>
       <c r="I266" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J266" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>760</v>
+        <v>162</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>761</v>
+        <v>654</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>762</v>
+        <v>655</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="O266" t="s" s="2">
-        <v>764</v>
+        <v>657</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>73</v>
@@ -30082,13 +30092,13 @@
         <v>73</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>73</v>
+        <v>285</v>
       </c>
       <c r="Y266" t="s" s="2">
-        <v>73</v>
+        <v>658</v>
       </c>
       <c r="Z266" t="s" s="2">
-        <v>73</v>
+        <v>659</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>73</v>
@@ -30106,7 +30116,7 @@
         <v>73</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>759</v>
+        <v>660</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>74</v>
@@ -30118,15 +30128,15 @@
         <v>93</v>
       </c>
       <c r="AJ266" t="s" s="2">
-        <v>323</v>
+        <v>94</v>
       </c>
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>765</v>
+        <v>661</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -30146,18 +30156,20 @@
         <v>73</v>
       </c>
       <c r="J267" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>96</v>
+        <v>662</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>97</v>
+        <v>663</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N267" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
         <v>73</v>
@@ -30206,7 +30218,7 @@
         <v>73</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>99</v>
+        <v>666</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>74</v>
@@ -30215,29 +30227,29 @@
         <v>81</v>
       </c>
       <c r="AI267" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ267" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>766</v>
+        <v>667</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H268" t="s" s="2">
         <v>73</v>
@@ -30246,19 +30258,19 @@
         <v>73</v>
       </c>
       <c r="J268" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>103</v>
+        <v>668</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>104</v>
+        <v>669</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" t="s" s="2">
@@ -30296,39 +30308,39 @@
         <v>73</v>
       </c>
       <c r="AB268" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC268" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD268" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE268" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>109</v>
+        <v>670</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH268" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI268" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ268" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -30339,30 +30351,32 @@
         <v>74</v>
       </c>
       <c r="G269" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H269" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I269" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J269" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>96</v>
+        <v>760</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="O269" s="2"/>
+        <v>763</v>
+      </c>
+      <c r="O269" t="s" s="2">
+        <v>764</v>
+      </c>
       <c r="P269" t="s" s="2">
         <v>73</v>
       </c>
@@ -30410,27 +30424,27 @@
         <v>73</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH269" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI269" t="s" s="2">
-        <v>772</v>
+        <v>93</v>
       </c>
       <c r="AJ269" t="s" s="2">
-        <v>94</v>
+        <v>765</v>
       </c>
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -30453,18 +30467,20 @@
         <v>82</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>128</v>
+        <v>767</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O270" s="2"/>
+        <v>770</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>771</v>
+      </c>
       <c r="P270" t="s" s="2">
         <v>73</v>
       </c>
@@ -30488,13 +30504,13 @@
         <v>73</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y270" t="s" s="2">
-        <v>777</v>
+        <v>73</v>
       </c>
       <c r="Z270" t="s" s="2">
-        <v>488</v>
+        <v>73</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>73</v>
@@ -30512,7 +30528,7 @@
         <v>73</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>74</v>
@@ -30524,15 +30540,15 @@
         <v>93</v>
       </c>
       <c r="AJ270" t="s" s="2">
-        <v>94</v>
+        <v>323</v>
       </c>
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -30552,20 +30568,18 @@
         <v>73</v>
       </c>
       <c r="J271" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>271</v>
+        <v>96</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>780</v>
+        <v>97</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="N271" t="s" s="2">
-        <v>782</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N271" s="2"/>
       <c r="O271" s="2"/>
       <c r="P271" t="s" s="2">
         <v>73</v>
@@ -30614,7 +30628,7 @@
         <v>73</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>783</v>
+        <v>99</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>74</v>
@@ -30623,29 +30637,29 @@
         <v>81</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ271" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G272" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H272" t="s" s="2">
         <v>73</v>
@@ -30654,19 +30668,19 @@
         <v>73</v>
       </c>
       <c r="J272" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>785</v>
+        <v>103</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>786</v>
+        <v>104</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>787</v>
+        <v>105</v>
       </c>
       <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
@@ -30704,39 +30718,39 @@
         <v>73</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC272" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD272" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>788</v>
+        <v>109</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH272" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI272" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -30747,7 +30761,7 @@
         <v>74</v>
       </c>
       <c r="G273" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H273" t="s" s="2">
         <v>73</v>
@@ -30756,23 +30770,21 @@
         <v>73</v>
       </c>
       <c r="J273" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>790</v>
+        <v>96</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="O273" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="O273" s="2"/>
       <c r="P273" t="s" s="2">
         <v>73</v>
       </c>
@@ -30820,16 +30832,16 @@
         <v>73</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH273" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>93</v>
+        <v>779</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>94</v>
@@ -30837,10 +30849,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30860,18 +30872,20 @@
         <v>73</v>
       </c>
       <c r="J274" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>97</v>
+        <v>781</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N274" s="2"/>
+        <v>782</v>
+      </c>
+      <c r="N274" t="s" s="2">
+        <v>783</v>
+      </c>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
         <v>73</v>
@@ -30896,13 +30910,13 @@
         <v>73</v>
       </c>
       <c r="X274" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y274" t="s" s="2">
-        <v>73</v>
+        <v>784</v>
       </c>
       <c r="Z274" t="s" s="2">
-        <v>73</v>
+        <v>488</v>
       </c>
       <c r="AA274" t="s" s="2">
         <v>73</v>
@@ -30920,7 +30934,7 @@
         <v>73</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>99</v>
+        <v>785</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>74</v>
@@ -30929,29 +30943,29 @@
         <v>81</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G275" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H275" t="s" s="2">
         <v>73</v>
@@ -30960,19 +30974,19 @@
         <v>73</v>
       </c>
       <c r="J275" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>103</v>
+        <v>787</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>104</v>
+        <v>788</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>105</v>
+        <v>789</v>
       </c>
       <c r="O275" s="2"/>
       <c r="P275" t="s" s="2">
@@ -31010,75 +31024,73 @@
         <v>73</v>
       </c>
       <c r="AB275" t="s" s="2">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="AC275" t="s" s="2">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="AD275" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE275" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>109</v>
+        <v>790</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH275" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI275" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ275" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
-        <v>798</v>
+        <v>73</v>
       </c>
       <c r="E276" s="2"/>
       <c r="F276" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G276" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H276" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I276" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J276" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O276" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>794</v>
+      </c>
+      <c r="O276" s="2"/>
       <c r="P276" t="s" s="2">
         <v>73</v>
       </c>
@@ -31126,27 +31138,27 @@
         <v>73</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI276" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ276" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -31157,7 +31169,7 @@
         <v>74</v>
       </c>
       <c r="G277" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H277" t="s" s="2">
         <v>73</v>
@@ -31169,19 +31181,19 @@
         <v>73</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>290</v>
+        <v>797</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="O277" t="s" s="2">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="P277" t="s" s="2">
         <v>73</v>
@@ -31206,13 +31218,13 @@
         <v>73</v>
       </c>
       <c r="X277" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="Y277" t="s" s="2">
-        <v>807</v>
+        <v>73</v>
       </c>
       <c r="Z277" t="s" s="2">
-        <v>808</v>
+        <v>73</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>73</v>
@@ -31230,13 +31242,13 @@
         <v>73</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH277" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI277" t="s" s="2">
         <v>93</v>
@@ -31247,10 +31259,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -31273,20 +31285,16 @@
         <v>73</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>810</v>
+        <v>96</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>811</v>
+        <v>97</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="N278" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="O278" t="s" s="2">
-        <v>814</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="N278" s="2"/>
+      <c r="O278" s="2"/>
       <c r="P278" t="s" s="2">
         <v>73</v>
       </c>
@@ -31334,7 +31342,7 @@
         <v>73</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>809</v>
+        <v>99</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>74</v>
@@ -31343,22 +31351,22 @@
         <v>81</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ278" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E279" s="2"/>
       <c r="F279" t="s" s="2">
@@ -31377,18 +31385,18 @@
         <v>73</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>626</v>
+        <v>102</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>674</v>
+        <v>103</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N279" s="2"/>
-      <c r="O279" t="s" s="2">
-        <v>816</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N279" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
         <v>73</v>
       </c>
@@ -31424,19 +31432,19 @@
         <v>73</v>
       </c>
       <c r="AB279" t="s" s="2">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AC279" t="s" s="2">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AD279" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE279" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>815</v>
+        <v>109</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>74</v>
@@ -31448,50 +31456,50 @@
         <v>93</v>
       </c>
       <c r="AJ279" t="s" s="2">
-        <v>817</v>
+        <v>110</v>
       </c>
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
-        <v>73</v>
+        <v>805</v>
       </c>
       <c r="E280" s="2"/>
       <c r="F280" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G280" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H280" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I280" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J280" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>819</v>
+        <v>102</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>755</v>
+        <v>807</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>756</v>
+        <v>105</v>
       </c>
       <c r="O280" t="s" s="2">
-        <v>821</v>
+        <v>268</v>
       </c>
       <c r="P280" t="s" s="2">
         <v>73</v>
@@ -31540,27 +31548,27 @@
         <v>73</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH280" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI280" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ280" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -31571,10 +31579,10 @@
         <v>74</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H281" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I281" t="s" s="2">
         <v>73</v>
@@ -31583,19 +31591,19 @@
         <v>73</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>823</v>
+        <v>290</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>763</v>
+        <v>812</v>
       </c>
       <c r="O281" t="s" s="2">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="P281" t="s" s="2">
         <v>73</v>
@@ -31620,13 +31628,13 @@
         <v>73</v>
       </c>
       <c r="X281" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Y281" t="s" s="2">
-        <v>73</v>
+        <v>814</v>
       </c>
       <c r="Z281" t="s" s="2">
-        <v>73</v>
+        <v>815</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>73</v>
@@ -31644,23 +31652,437 @@
         <v>73</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH281" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI281" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ281" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="282" hidden="true">
+      <c r="A282" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="C282" s="2"/>
+      <c r="D282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E282" s="2"/>
+      <c r="F282" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G282" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K282" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="L282" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="M282" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="N282" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="O282" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="P282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q282" s="2"/>
+      <c r="R282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE282" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF282" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AG282" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH282" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI282" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ282" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="283" hidden="true">
+      <c r="A283" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="C283" s="2"/>
+      <c r="D283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E283" s="2"/>
+      <c r="F283" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G283" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K283" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L283" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M283" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N283" s="2"/>
+      <c r="O283" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="P283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q283" s="2"/>
+      <c r="R283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE283" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF283" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AG283" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH283" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI283" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ283" t="s" s="2">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="284" hidden="true">
+      <c r="A284" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="C284" s="2"/>
+      <c r="D284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E284" s="2"/>
+      <c r="F284" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G284" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K284" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="L284" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="M284" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N284" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="O284" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="P284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q284" s="2"/>
+      <c r="R284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE284" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF284" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="AG284" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH284" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI284" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ284" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="285" hidden="true">
+      <c r="A285" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="C285" s="2"/>
+      <c r="D285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E285" s="2"/>
+      <c r="F285" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G285" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H285" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K285" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="L285" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="M285" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="N285" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="O285" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="P285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q285" s="2"/>
+      <c r="R285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE285" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF285" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AG285" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH285" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI285" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ285" t="s" s="2">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ281">
+  <autoFilter ref="A1:AJ285">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -31670,7 +32092,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI280">
+  <conditionalFormatting sqref="A2:AI284">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
